--- a/Side Bar Files/GWD Data/PVC on Wall PRICE.xlsx
+++ b/Side Bar Files/GWD Data/PVC on Wall PRICE.xlsx
@@ -594,9 +594,15 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1035,7 +1041,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7E4E814-48B5-4F4B-B3F5-AD51A955B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FC190FD-71C8-4739-BA4D-50FDDFDEB9A7}">
   <dimension ref="A1:G947"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/PVC on Wall PRICE.xlsx
+++ b/Side Bar Files/GWD Data/PVC on Wall PRICE.xlsx
@@ -1045,7 +1045,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D95FFB0-E67C-4A21-B4A9-CFE1B37DBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C16F4B06-F26F-4C2D-AB72-3050322FBAA6}">
   <dimension ref="A1:I947"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
